--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/85.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/85.xlsx
@@ -426,13 +426,13 @@
         <v>-6.882702809403036</v>
       </c>
       <c r="E2">
-        <v>-13.01514883945874</v>
+        <v>-10.95595208174286</v>
       </c>
       <c r="F2">
-        <v>-1.244839202213298</v>
+        <v>-1.633375820454976</v>
       </c>
       <c r="G2">
-        <v>-15.75174731961591</v>
+        <v>-12.5012501106088</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.052685726806576</v>
       </c>
       <c r="E3">
-        <v>-12.74154749686331</v>
+        <v>-11.85001776202523</v>
       </c>
       <c r="F3">
-        <v>-1.19285334911581</v>
+        <v>-1.447124036874729</v>
       </c>
       <c r="G3">
-        <v>-15.30608167911923</v>
+        <v>-11.94600872330777</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.231182898080202</v>
       </c>
       <c r="E4">
-        <v>-14.1903512430853</v>
+        <v>-12.69771186846906</v>
       </c>
       <c r="F4">
-        <v>-1.35443717980809</v>
+        <v>-1.164804000489616</v>
       </c>
       <c r="G4">
-        <v>-15.4154753459189</v>
+        <v>-12.24807614049303</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.505060847456249</v>
       </c>
       <c r="E5">
-        <v>-16.06034835676072</v>
+        <v>-12.67208070558565</v>
       </c>
       <c r="F5">
-        <v>-0.8284155953563758</v>
+        <v>-1.235922655489565</v>
       </c>
       <c r="G5">
-        <v>-14.93580212637005</v>
+        <v>-11.30180966682099</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.852935204589406</v>
       </c>
       <c r="E6">
-        <v>-15.73265892061767</v>
+        <v>-13.90752539893625</v>
       </c>
       <c r="F6">
-        <v>-0.5129418104090177</v>
+        <v>-0.9696961410060398</v>
       </c>
       <c r="G6">
-        <v>-13.93552906804311</v>
+        <v>-10.48310513386815</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.274647000190535</v>
       </c>
       <c r="E7">
-        <v>-15.98314240340394</v>
+        <v>-14.4341189989182</v>
       </c>
       <c r="F7">
-        <v>-0.5501934925129114</v>
+        <v>-0.8163197745406974</v>
       </c>
       <c r="G7">
-        <v>-14.06618636884153</v>
+        <v>-10.67345157073963</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.753694229380984</v>
       </c>
       <c r="E8">
-        <v>-16.66775710388355</v>
+        <v>-15.08635511024296</v>
       </c>
       <c r="F8">
-        <v>-0.06414974728770427</v>
+        <v>-1.022231201691584</v>
       </c>
       <c r="G8">
-        <v>-12.77162567534661</v>
+        <v>-10.29261634353849</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.286451516584683</v>
       </c>
       <c r="E9">
-        <v>-16.53685703421783</v>
+        <v>-15.28453018976663</v>
       </c>
       <c r="F9">
-        <v>-0.3665916562542206</v>
+        <v>-0.6139802676306817</v>
       </c>
       <c r="G9">
-        <v>-12.3424465516355</v>
+        <v>-9.293457283785509</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.8562826324979</v>
       </c>
       <c r="E10">
-        <v>-17.25381862453422</v>
+        <v>-16.98891195203352</v>
       </c>
       <c r="F10">
-        <v>-0.01138191536197296</v>
+        <v>-0.5006943983586269</v>
       </c>
       <c r="G10">
-        <v>-12.32107366963396</v>
+        <v>-9.049880585188093</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.463072535637926</v>
       </c>
       <c r="E11">
-        <v>-17.14695569490122</v>
+        <v>-16.59358069963791</v>
       </c>
       <c r="F11">
-        <v>0.3956256392273277</v>
+        <v>-0.3229250969830474</v>
       </c>
       <c r="G11">
-        <v>-11.82681584171185</v>
+        <v>-8.653058733577813</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.102836570316051</v>
       </c>
       <c r="E12">
-        <v>-18.52093546509447</v>
+        <v>-18.16980211901372</v>
       </c>
       <c r="F12">
-        <v>0.5757292799439963</v>
+        <v>0.1912292960561609</v>
       </c>
       <c r="G12">
-        <v>-11.5445090708505</v>
+        <v>-7.833894034795011</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.7728224233863138</v>
       </c>
       <c r="E13">
-        <v>-19.67696430977256</v>
+        <v>-18.15264825947267</v>
       </c>
       <c r="F13">
-        <v>0.7289822196663216</v>
+        <v>-0.04890198850437377</v>
       </c>
       <c r="G13">
-        <v>-10.73219058024291</v>
+        <v>-8.110354382234009</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.4821730733834301</v>
       </c>
       <c r="E14">
-        <v>-19.9422468456159</v>
+        <v>-18.89232467541154</v>
       </c>
       <c r="F14">
-        <v>0.6530524067909133</v>
+        <v>0.3816850442056148</v>
       </c>
       <c r="G14">
-        <v>-11.51485982500079</v>
+        <v>-6.733405797176022</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.2341271540853557</v>
       </c>
       <c r="E15">
-        <v>-20.92998401074694</v>
+        <v>-19.97923542131055</v>
       </c>
       <c r="F15">
-        <v>1.377284086649687</v>
+        <v>0.6730276583420206</v>
       </c>
       <c r="G15">
-        <v>-10.54857448245278</v>
+        <v>-7.01749695208304</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.03369394278927642</v>
       </c>
       <c r="E16">
-        <v>-22.21111647836092</v>
+        <v>-20.76899675977425</v>
       </c>
       <c r="F16">
-        <v>1.433361246349603</v>
+        <v>0.8292875717365081</v>
       </c>
       <c r="G16">
-        <v>-10.55575174518192</v>
+        <v>-6.732247106237278</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.1137160980818276</v>
       </c>
       <c r="E17">
-        <v>-22.12181044245566</v>
+        <v>-21.41961167740427</v>
       </c>
       <c r="F17">
-        <v>1.534910806258794</v>
+        <v>0.7258460206793227</v>
       </c>
       <c r="G17">
-        <v>-10.10467667327406</v>
+        <v>-6.351789281227615</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.2114134975710674</v>
       </c>
       <c r="E18">
-        <v>-22.86132836180426</v>
+        <v>-22.18889072793128</v>
       </c>
       <c r="F18">
-        <v>1.64695412442665</v>
+        <v>1.280477758488926</v>
       </c>
       <c r="G18">
-        <v>-9.809634233723134</v>
+        <v>-5.775578898480846</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.2654042371844723</v>
       </c>
       <c r="E19">
-        <v>-23.99968710090442</v>
+        <v>-24.08114529135439</v>
       </c>
       <c r="F19">
-        <v>2.207379463851433</v>
+        <v>1.405006230151776</v>
       </c>
       <c r="G19">
-        <v>-8.712257908911059</v>
+        <v>-5.734746629799476</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.2865128445451615</v>
       </c>
       <c r="E20">
-        <v>-25.48888936374884</v>
+        <v>-23.66394603797574</v>
       </c>
       <c r="F20">
-        <v>2.002714729641759</v>
+        <v>1.821161445970191</v>
       </c>
       <c r="G20">
-        <v>-9.430275509832509</v>
+        <v>-5.124815030189692</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.2900230945647606</v>
       </c>
       <c r="E21">
-        <v>-25.69238992870553</v>
+        <v>-23.44299273419348</v>
       </c>
       <c r="F21">
-        <v>1.869501654127959</v>
+        <v>1.826022305889819</v>
       </c>
       <c r="G21">
-        <v>-8.971020079897114</v>
+        <v>-5.446689441336411</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.2887384151187419</v>
       </c>
       <c r="E22">
-        <v>-25.28080145462238</v>
+        <v>-25.14888700677894</v>
       </c>
       <c r="F22">
-        <v>2.421033641116287</v>
+        <v>2.147803280242092</v>
       </c>
       <c r="G22">
-        <v>-8.251847098582459</v>
+        <v>-5.19141327480321</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.293549454001767</v>
       </c>
       <c r="E23">
-        <v>-26.30462602912054</v>
+        <v>-24.2041250599807</v>
       </c>
       <c r="F23">
-        <v>2.711959586449085</v>
+        <v>2.331066314233038</v>
       </c>
       <c r="G23">
-        <v>-8.534130695625034</v>
+        <v>-5.49270933487782</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.3109352539866825</v>
       </c>
       <c r="E24">
-        <v>-27.11984191998135</v>
+        <v>-25.82123859964577</v>
       </c>
       <c r="F24">
-        <v>2.888859102051724</v>
+        <v>2.14963728567189</v>
       </c>
       <c r="G24">
-        <v>-8.781766123053599</v>
+        <v>-4.769130017450395</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.340297905054049</v>
       </c>
       <c r="E25">
-        <v>-25.32707340203275</v>
+        <v>-25.35469709347954</v>
       </c>
       <c r="F25">
-        <v>2.474582623502858</v>
+        <v>1.955351995019294</v>
       </c>
       <c r="G25">
-        <v>-7.763237061350346</v>
+        <v>-5.175181670024164</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.3770931483724246</v>
       </c>
       <c r="E26">
-        <v>-26.33954962066769</v>
+        <v>-25.63899469168109</v>
       </c>
       <c r="F26">
-        <v>2.494766623639471</v>
+        <v>2.397451677893391</v>
       </c>
       <c r="G26">
-        <v>-8.336318978562502</v>
+        <v>-4.409349859879021</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.4125132570600603</v>
       </c>
       <c r="E27">
-        <v>-26.65674658253496</v>
+        <v>-26.14436333398908</v>
       </c>
       <c r="F27">
-        <v>2.302686447013127</v>
+        <v>2.04849031232046</v>
       </c>
       <c r="G27">
-        <v>-8.103432031511392</v>
+        <v>-4.762628106011267</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.4364638414550043</v>
       </c>
       <c r="E28">
-        <v>-26.59565293969748</v>
+        <v>-26.04667509269562</v>
       </c>
       <c r="F28">
-        <v>2.396616683551369</v>
+        <v>2.281145581070729</v>
       </c>
       <c r="G28">
-        <v>-8.063983570865437</v>
+        <v>-5.749597737088647</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.4388191072975899</v>
       </c>
       <c r="E29">
-        <v>-26.25641136636087</v>
+        <v>-26.08763061162099</v>
       </c>
       <c r="F29">
-        <v>2.311569859040749</v>
+        <v>2.338798295570769</v>
       </c>
       <c r="G29">
-        <v>-8.17221192563529</v>
+        <v>-4.733048381617879</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.4093255558845521</v>
       </c>
       <c r="E30">
-        <v>-26.15207532522415</v>
+        <v>-25.67853732671606</v>
       </c>
       <c r="F30">
-        <v>2.487472020290419</v>
+        <v>1.970141666628877</v>
       </c>
       <c r="G30">
-        <v>-8.47096879728128</v>
+        <v>-5.901435908247319</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.3411584274213353</v>
       </c>
       <c r="E31">
-        <v>-25.50083094970707</v>
+        <v>-25.29698622072579</v>
       </c>
       <c r="F31">
-        <v>2.227999185241918</v>
+        <v>2.193766073953826</v>
       </c>
       <c r="G31">
-        <v>-8.588360742103836</v>
+        <v>-5.400984049621234</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.2279756003283342</v>
       </c>
       <c r="E32">
-        <v>-25.87975554077289</v>
+        <v>-24.36027137223918</v>
       </c>
       <c r="F32">
-        <v>2.071205803240028</v>
+        <v>2.479519693223543</v>
       </c>
       <c r="G32">
-        <v>-7.710655666550102</v>
+        <v>-5.497453346635596</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.06627167098562176</v>
       </c>
       <c r="E33">
-        <v>-24.98375620208924</v>
+        <v>-23.27706944655244</v>
       </c>
       <c r="F33">
-        <v>2.145662778873259</v>
+        <v>2.38294365120076</v>
       </c>
       <c r="G33">
-        <v>-8.514793799130151</v>
+        <v>-5.826107755046743</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.1411432191248443</v>
       </c>
       <c r="E34">
-        <v>-24.54253339409989</v>
+        <v>-24.51766301484977</v>
       </c>
       <c r="F34">
-        <v>2.236683789092868</v>
+        <v>2.580933400878676</v>
       </c>
       <c r="G34">
-        <v>-7.897052622593227</v>
+        <v>-5.548544995943169</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.3916223555532543</v>
       </c>
       <c r="E35">
-        <v>-23.45600756849153</v>
+        <v>-24.20767538360271</v>
       </c>
       <c r="F35">
-        <v>2.42390476253439</v>
+        <v>2.26069650336522</v>
       </c>
       <c r="G35">
-        <v>-8.68550539040821</v>
+        <v>-5.332207466042875</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.6771622581706516</v>
       </c>
       <c r="E36">
-        <v>-23.67031307243052</v>
+        <v>-23.04430588255819</v>
       </c>
       <c r="F36">
-        <v>2.017724746980486</v>
+        <v>2.525928148597983</v>
       </c>
       <c r="G36">
-        <v>-8.674170082481746</v>
+        <v>-6.426541399504358</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.986003835695402</v>
       </c>
       <c r="E37">
-        <v>-22.96422434820655</v>
+        <v>-22.08083680963426</v>
       </c>
       <c r="F37">
-        <v>2.468603467589451</v>
+        <v>2.42349057883299</v>
       </c>
       <c r="G37">
-        <v>-8.975608496014544</v>
+        <v>-6.147465721089336</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.308413462314037</v>
       </c>
       <c r="E38">
-        <v>-22.83486395970343</v>
+        <v>-22.31420266067153</v>
       </c>
       <c r="F38">
-        <v>2.572142766000167</v>
+        <v>2.530431153799601</v>
       </c>
       <c r="G38">
-        <v>-8.87106146788436</v>
+        <v>-7.420483039487443</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.630579508792798</v>
       </c>
       <c r="E39">
-        <v>-22.18445282340376</v>
+        <v>-21.89095336601863</v>
       </c>
       <c r="F39">
-        <v>2.303077436427249</v>
+        <v>2.635131823309042</v>
       </c>
       <c r="G39">
-        <v>-9.546866302634562</v>
+        <v>-6.09789361218429</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.939981075067915</v>
       </c>
       <c r="E40">
-        <v>-21.97418218980561</v>
+        <v>-21.36785574797061</v>
       </c>
       <c r="F40">
-        <v>2.436860428714174</v>
+        <v>2.7710254957383</v>
       </c>
       <c r="G40">
-        <v>-9.105199801149315</v>
+        <v>-6.780534723473087</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.227452786300313</v>
       </c>
       <c r="E41">
-        <v>-21.96253495465788</v>
+        <v>-20.6027111942126</v>
       </c>
       <c r="F41">
-        <v>2.713762113917576</v>
+        <v>2.343274793015497</v>
       </c>
       <c r="G41">
-        <v>-9.032288346192406</v>
+        <v>-6.715393118896848</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.482353710147004</v>
       </c>
       <c r="E42">
-        <v>-19.45709331127814</v>
+        <v>-20.07175667376126</v>
       </c>
       <c r="F42">
-        <v>2.562946231094287</v>
+        <v>2.779448335489966</v>
       </c>
       <c r="G42">
-        <v>-9.781656813370754</v>
+        <v>-7.202490236817514</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.700985861766913</v>
       </c>
       <c r="E43">
-        <v>-19.27733553554367</v>
+        <v>-20.44709471341302</v>
       </c>
       <c r="F43">
-        <v>2.763492322577242</v>
+        <v>2.69908675700958</v>
       </c>
       <c r="G43">
-        <v>-9.641888891248263</v>
+        <v>-6.535474900474076</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.882125595061992</v>
       </c>
       <c r="E44">
-        <v>-20.27742637776763</v>
+        <v>-19.14321119238449</v>
       </c>
       <c r="F44">
-        <v>2.543463029780443</v>
+        <v>2.525696205725199</v>
       </c>
       <c r="G44">
-        <v>-9.719832375424863</v>
+        <v>-6.380031545223138</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.024358469647908</v>
       </c>
       <c r="E45">
-        <v>-18.69700706298671</v>
+        <v>-18.11884320100541</v>
       </c>
       <c r="F45">
-        <v>2.71935856409089</v>
+        <v>2.509692147503112</v>
       </c>
       <c r="G45">
-        <v>-9.979524809707453</v>
+        <v>-6.854700875189379</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.135412034843407</v>
       </c>
       <c r="E46">
-        <v>-18.414978230263</v>
+        <v>-18.59743950498006</v>
       </c>
       <c r="F46">
-        <v>2.606465340967762</v>
+        <v>2.664089890976107</v>
       </c>
       <c r="G46">
-        <v>-9.697370323940909</v>
+        <v>-7.557076148437772</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.223997604670661</v>
       </c>
       <c r="E47">
-        <v>-17.83735325668862</v>
+        <v>-17.46714144961355</v>
       </c>
       <c r="F47">
-        <v>2.77899107668362</v>
+        <v>2.530795635456833</v>
       </c>
       <c r="G47">
-        <v>-10.27410708342842</v>
+        <v>-7.202963644829629</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.299255782498643</v>
       </c>
       <c r="E48">
-        <v>-17.64355721153036</v>
+        <v>-17.80739740112788</v>
       </c>
       <c r="F48">
-        <v>2.702748140929954</v>
+        <v>2.93139908165509</v>
       </c>
       <c r="G48">
-        <v>-10.54684968822682</v>
+        <v>-6.711913735535074</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.377336255487887</v>
       </c>
       <c r="E49">
-        <v>-17.41514098258347</v>
+        <v>-16.9636883518108</v>
       </c>
       <c r="F49">
-        <v>2.510894936971977</v>
+        <v>2.684749374001926</v>
       </c>
       <c r="G49">
-        <v>-10.29084851222052</v>
+        <v>-6.746902891339631</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.468631333802877</v>
       </c>
       <c r="E50">
-        <v>-16.74838205511611</v>
+        <v>-15.79722137454503</v>
       </c>
       <c r="F50">
-        <v>2.787478529092704</v>
+        <v>2.190600053740326</v>
       </c>
       <c r="G50">
-        <v>-10.68945143733092</v>
+        <v>-6.565902124525518</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.583003751114626</v>
       </c>
       <c r="E51">
-        <v>-16.41081148868833</v>
+        <v>-16.53416712065727</v>
       </c>
       <c r="F51">
-        <v>2.741119775762433</v>
+        <v>2.612780814046705</v>
       </c>
       <c r="G51">
-        <v>-10.81918840646942</v>
+        <v>-7.590595422022893</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.733392544706879</v>
       </c>
       <c r="E52">
-        <v>-15.87634287240705</v>
+        <v>-14.91895101160141</v>
       </c>
       <c r="F52">
-        <v>2.501093693862054</v>
+        <v>2.268327423879809</v>
       </c>
       <c r="G52">
-        <v>-10.68750483655383</v>
+        <v>-6.893358115451449</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.919859102992055</v>
       </c>
       <c r="E53">
-        <v>-16.02641197254723</v>
+        <v>-14.78538367074517</v>
       </c>
       <c r="F53">
-        <v>2.557503857257894</v>
+        <v>2.508045353106347</v>
       </c>
       <c r="G53">
-        <v>-10.42695166043103</v>
+        <v>-7.048149293231152</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.146978741574812</v>
       </c>
       <c r="E54">
-        <v>-14.82665618285108</v>
+        <v>-14.95886498150502</v>
       </c>
       <c r="F54">
-        <v>2.067930438529359</v>
+        <v>2.623783189890688</v>
       </c>
       <c r="G54">
-        <v>-10.28950443073157</v>
+        <v>-7.003768119731682</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.416802111619089</v>
       </c>
       <c r="E55">
-        <v>-15.07682720093082</v>
+        <v>-14.4350654499858</v>
       </c>
       <c r="F55">
-        <v>2.413391123458059</v>
+        <v>2.6553887197771</v>
       </c>
       <c r="G55">
-        <v>-10.90619947487809</v>
+        <v>-7.281407021382661</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.719236617523605</v>
       </c>
       <c r="E56">
-        <v>-14.69496815870803</v>
+        <v>-13.44849663114875</v>
       </c>
       <c r="F56">
-        <v>2.64826641684783</v>
+        <v>1.952396380126106</v>
       </c>
       <c r="G56">
-        <v>-11.07612646686334</v>
+        <v>-7.278401046033002</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.052993418942616</v>
       </c>
       <c r="E57">
-        <v>-14.15998782486387</v>
+        <v>-13.81441544486454</v>
       </c>
       <c r="F57">
-        <v>2.347482899421719</v>
+        <v>2.657852284433027</v>
       </c>
       <c r="G57">
-        <v>-10.89530446950834</v>
+        <v>-6.601480557436066</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.409891404971869</v>
       </c>
       <c r="E58">
-        <v>-14.2700523856203</v>
+        <v>-12.98345404987905</v>
       </c>
       <c r="F58">
-        <v>2.655464929578158</v>
+        <v>2.216965331436629</v>
       </c>
       <c r="G58">
-        <v>-11.13850376591428</v>
+        <v>-8.112373815012964</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.776411207786533</v>
       </c>
       <c r="E59">
-        <v>-14.26985313276396</v>
+        <v>-12.63879189315526</v>
       </c>
       <c r="F59">
-        <v>3.000938868385303</v>
+        <v>2.579733924879422</v>
       </c>
       <c r="G59">
-        <v>-11.03195716827838</v>
+        <v>-7.844971120169412</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.148034719213696</v>
       </c>
       <c r="E60">
-        <v>-13.37277601726649</v>
+        <v>-12.59275995486729</v>
       </c>
       <c r="F60">
-        <v>2.735110798622525</v>
+        <v>2.715594462612569</v>
       </c>
       <c r="G60">
-        <v>-10.74548242058309</v>
+        <v>-8.467085527363714</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.509847158261182</v>
       </c>
       <c r="E61">
-        <v>-15.15448147321435</v>
+        <v>-12.10921855727627</v>
       </c>
       <c r="F61">
-        <v>2.899584803183172</v>
+        <v>2.63597178785548</v>
       </c>
       <c r="G61">
-        <v>-11.25097955061102</v>
+        <v>-8.181342410232601</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.849397177346635</v>
       </c>
       <c r="E62">
-        <v>-13.57384932015507</v>
+        <v>-12.39842954977614</v>
       </c>
       <c r="F62">
-        <v>2.512528477490298</v>
+        <v>2.696699402154712</v>
       </c>
       <c r="G62">
-        <v>-10.78461968994835</v>
+        <v>-7.762157823504544</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.161269116269025</v>
       </c>
       <c r="E63">
-        <v>-13.32550780557443</v>
+        <v>-10.66484365863378</v>
       </c>
       <c r="F63">
-        <v>2.476424912606684</v>
+        <v>2.074239284669079</v>
       </c>
       <c r="G63">
-        <v>-11.72990955268631</v>
+        <v>-8.203430370070619</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.428613803636394</v>
       </c>
       <c r="E64">
-        <v>-12.3992944883116</v>
+        <v>-11.77209630977525</v>
       </c>
       <c r="F64">
-        <v>2.618431936468604</v>
+        <v>2.246529764042543</v>
       </c>
       <c r="G64">
-        <v>-10.89180522287334</v>
+        <v>-8.610591055400041</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.646741394144214</v>
       </c>
       <c r="E65">
-        <v>-12.61174331790745</v>
+        <v>-10.64626785825431</v>
       </c>
       <c r="F65">
-        <v>2.301892871041245</v>
+        <v>2.442829644218747</v>
       </c>
       <c r="G65">
-        <v>-10.80068907799597</v>
+        <v>-8.628888440595594</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.812364074883934</v>
       </c>
       <c r="E66">
-        <v>-12.09379910328015</v>
+        <v>-11.62865236710828</v>
       </c>
       <c r="F66">
-        <v>2.637676567970442</v>
+        <v>2.362570783296309</v>
       </c>
       <c r="G66">
-        <v>-11.41680808721866</v>
+        <v>-8.999073642796898</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.915644624643046</v>
       </c>
       <c r="E67">
-        <v>-13.67922691031356</v>
+        <v>-11.26984325758453</v>
       </c>
       <c r="F67">
-        <v>2.544453757194191</v>
+        <v>2.090909350283017</v>
       </c>
       <c r="G67">
-        <v>-11.09954526600814</v>
+        <v>-9.129856744325807</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.959293849535494</v>
       </c>
       <c r="E68">
-        <v>-12.49873072057203</v>
+        <v>-10.69619428418888</v>
       </c>
       <c r="F68">
-        <v>2.027342092526988</v>
+        <v>2.308521466998447</v>
       </c>
       <c r="G68">
-        <v>-11.01406366963862</v>
+        <v>-8.659669893019737</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.943518774885269</v>
       </c>
       <c r="E69">
-        <v>-12.37514413642869</v>
+        <v>-10.64266772141822</v>
       </c>
       <c r="F69">
-        <v>2.340670405901096</v>
+        <v>2.12560137711226</v>
       </c>
       <c r="G69">
-        <v>-11.22613390633879</v>
+        <v>-8.495625740457772</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.866562788978177</v>
       </c>
       <c r="E70">
-        <v>-12.92300797882467</v>
+        <v>-11.52336987490395</v>
       </c>
       <c r="F70">
-        <v>2.687693391751476</v>
+        <v>2.23446210771856</v>
       </c>
       <c r="G70">
-        <v>-10.98513612271647</v>
+        <v>-8.211041314265403</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.738532094791965</v>
       </c>
       <c r="E71">
-        <v>-12.50564117190773</v>
+        <v>-10.60103293139169</v>
       </c>
       <c r="F71">
-        <v>2.691884930809641</v>
+        <v>1.787892554338958</v>
       </c>
       <c r="G71">
-        <v>-11.47078984278201</v>
+        <v>-8.237843490951342</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.562374350673009</v>
       </c>
       <c r="E72">
-        <v>-12.96562091923685</v>
+        <v>-10.72268585713375</v>
       </c>
       <c r="F72">
-        <v>2.067720033209048</v>
+        <v>2.065259782022733</v>
       </c>
       <c r="G72">
-        <v>-10.82431975205529</v>
+        <v>-8.511536222319508</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.342199757645965</v>
       </c>
       <c r="E73">
-        <v>-12.79387854249595</v>
+        <v>-11.3063110587683</v>
       </c>
       <c r="F73">
-        <v>2.189072544249564</v>
+        <v>1.98674546285059</v>
       </c>
       <c r="G73">
-        <v>-10.92414925279201</v>
+        <v>-8.168206165532773</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.092560687432842</v>
       </c>
       <c r="E74">
-        <v>-13.9825305139253</v>
+        <v>-11.7070674230251</v>
       </c>
       <c r="F74">
-        <v>2.245063553739588</v>
+        <v>1.897419292337108</v>
       </c>
       <c r="G74">
-        <v>-10.70085957725925</v>
+        <v>-8.679665588076935</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.815734287004617</v>
       </c>
       <c r="E75">
-        <v>-13.8697081124982</v>
+        <v>-10.58383378711056</v>
       </c>
       <c r="F75">
-        <v>2.035869306571406</v>
+        <v>2.23284347781349</v>
       </c>
       <c r="G75">
-        <v>-10.44917204209062</v>
+        <v>-8.115426138000172</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.520400077547231</v>
       </c>
       <c r="E76">
-        <v>-12.50701782800606</v>
+        <v>-12.01311528188549</v>
       </c>
       <c r="F76">
-        <v>2.407691955726798</v>
+        <v>1.872024861236887</v>
       </c>
       <c r="G76">
-        <v>-9.847242031049255</v>
+        <v>-7.808326691595219</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.21766869407599</v>
       </c>
       <c r="E77">
-        <v>-13.73134964614184</v>
+        <v>-11.83870563395407</v>
       </c>
       <c r="F77">
-        <v>2.038929295757348</v>
+        <v>2.057383664756915</v>
       </c>
       <c r="G77">
-        <v>-8.829577021731753</v>
+        <v>-7.840952117884737</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.907790159099273</v>
       </c>
       <c r="E78">
-        <v>-14.48856937038643</v>
+        <v>-12.92344724080341</v>
       </c>
       <c r="F78">
-        <v>1.782451837237371</v>
+        <v>1.784479680639424</v>
       </c>
       <c r="G78">
-        <v>-10.3666997316163</v>
+        <v>-7.275126916494663</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.599631117654792</v>
       </c>
       <c r="E79">
-        <v>-15.82133097016187</v>
+        <v>-12.37762121171089</v>
       </c>
       <c r="F79">
-        <v>2.145690943364954</v>
+        <v>1.532427360785201</v>
       </c>
       <c r="G79">
-        <v>-9.145287197084349</v>
+        <v>-6.66618848054666</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.297556875194578</v>
       </c>
       <c r="E80">
-        <v>-15.04895897188762</v>
+        <v>-14.00088441907838</v>
       </c>
       <c r="F80">
-        <v>1.662005560135517</v>
+        <v>1.764337098872951</v>
       </c>
       <c r="G80">
-        <v>-9.013947923904844</v>
+        <v>-6.284770597330609</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.998913141355882</v>
       </c>
       <c r="E81">
-        <v>-16.11623878296338</v>
+        <v>-15.17376824401302</v>
       </c>
       <c r="F81">
-        <v>1.88049740303272</v>
+        <v>1.752007678449683</v>
       </c>
       <c r="G81">
-        <v>-9.325470259150261</v>
+        <v>-5.823045500422917</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.71112607537372</v>
       </c>
       <c r="E82">
-        <v>-17.25785802334907</v>
+        <v>-14.25570165148999</v>
       </c>
       <c r="F82">
-        <v>2.287808968458848</v>
+        <v>1.733202081671329</v>
       </c>
       <c r="G82">
-        <v>-8.794538207744106</v>
+        <v>-6.856154204681119</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.432215329554393</v>
       </c>
       <c r="E83">
-        <v>-16.36203076667771</v>
+        <v>-15.76791309076739</v>
       </c>
       <c r="F83">
-        <v>1.80168818506518</v>
+        <v>1.606748484164373</v>
       </c>
       <c r="G83">
-        <v>-8.849731622974835</v>
+        <v>-5.939331723035357</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.159309854836394</v>
       </c>
       <c r="E84">
-        <v>-18.66685195456963</v>
+        <v>-17.21812972087977</v>
       </c>
       <c r="F84">
-        <v>1.708019712626224</v>
+        <v>1.663171901438658</v>
       </c>
       <c r="G84">
-        <v>-7.453432899239809</v>
+        <v>-5.263103138456128</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.899915266301121</v>
       </c>
       <c r="E85">
-        <v>-19.50104667999659</v>
+        <v>-18.51335932807964</v>
       </c>
       <c r="F85">
-        <v>1.701821867718478</v>
+        <v>1.537165622329214</v>
       </c>
       <c r="G85">
-        <v>-8.40260272134979</v>
+        <v>-6.210382639063186</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.651147302097124</v>
       </c>
       <c r="E86">
-        <v>-21.1126264244243</v>
+        <v>-19.54407171154347</v>
       </c>
       <c r="F86">
-        <v>2.120573186977267</v>
+        <v>1.576624075194166</v>
       </c>
       <c r="G86">
-        <v>-7.333369344167061</v>
+        <v>-5.440555000452142</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.418070182229693</v>
       </c>
       <c r="E87">
-        <v>-22.5137906240856</v>
+        <v>-20.19129933061575</v>
       </c>
       <c r="F87">
-        <v>1.887097834498226</v>
+        <v>1.594051268614262</v>
       </c>
       <c r="G87">
-        <v>-6.459805761082955</v>
+        <v>-5.091851928255169</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.208014120657968</v>
       </c>
       <c r="E88">
-        <v>-23.25919555964417</v>
+        <v>-21.16099958377423</v>
       </c>
       <c r="F88">
-        <v>1.946521598505452</v>
+        <v>1.682249202725131</v>
       </c>
       <c r="G88">
-        <v>-6.666582435465833</v>
+        <v>-4.94703211363975</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.022438965272633</v>
       </c>
       <c r="E89">
-        <v>-24.26631006505403</v>
+        <v>-23.93925914374606</v>
       </c>
       <c r="F89">
-        <v>1.891435166219285</v>
+        <v>1.474295849926343</v>
       </c>
       <c r="G89">
-        <v>-6.864407394710523</v>
+        <v>-4.334269997593889</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.873227442470421</v>
       </c>
       <c r="E90">
-        <v>-26.70617487632869</v>
+        <v>-24.8520772348942</v>
       </c>
       <c r="F90">
-        <v>1.691924533989829</v>
+        <v>1.359040122970431</v>
       </c>
       <c r="G90">
-        <v>-6.437088797592476</v>
+        <v>-4.780058128275529</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.767061432361033</v>
       </c>
       <c r="E91">
-        <v>-27.50565884848686</v>
+        <v>-26.83903124676572</v>
       </c>
       <c r="F91">
-        <v>1.899911021484729</v>
+        <v>1.227091136113303</v>
       </c>
       <c r="G91">
-        <v>-6.420678423354309</v>
+        <v>-4.730956116837059</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.70917640270425</v>
       </c>
       <c r="E92">
-        <v>-29.78898789873837</v>
+        <v>-29.93121821037128</v>
       </c>
       <c r="F92">
-        <v>1.59692073329756</v>
+        <v>1.064891828440744</v>
       </c>
       <c r="G92">
-        <v>-6.644977815276549</v>
+        <v>-4.071495445414239</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.712369436495228</v>
       </c>
       <c r="E93">
-        <v>-31.60779740646808</v>
+        <v>-31.12465904306374</v>
       </c>
       <c r="F93">
-        <v>1.791613580712333</v>
+        <v>1.035532830950723</v>
       </c>
       <c r="G93">
-        <v>-6.50784177685778</v>
+        <v>-4.42502529300747</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.776242585671924</v>
       </c>
       <c r="E94">
-        <v>-33.82831878647021</v>
+        <v>-32.56346165443979</v>
       </c>
       <c r="F94">
-        <v>1.554471874108502</v>
+        <v>1.169420197530402</v>
       </c>
       <c r="G94">
-        <v>-6.37497634218467</v>
+        <v>-4.722289108615247</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.903245676067219</v>
       </c>
       <c r="E95">
-        <v>-36.13043194690555</v>
+        <v>-35.59294057422414</v>
       </c>
       <c r="F95">
-        <v>1.107062356182461</v>
+        <v>0.8361895289366336</v>
       </c>
       <c r="G95">
-        <v>-6.946555271721998</v>
+        <v>-4.967593911984164</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.099554023634636</v>
       </c>
       <c r="E96">
-        <v>-38.00265706979273</v>
+        <v>-36.9207525519092</v>
       </c>
       <c r="F96">
-        <v>1.415814768023504</v>
+        <v>1.073824942512533</v>
       </c>
       <c r="G96">
-        <v>-7.325520040693449</v>
+        <v>-4.72200440169887</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.35122772674974</v>
       </c>
       <c r="E97">
-        <v>-40.05808613713423</v>
+        <v>-40.29331319098866</v>
       </c>
       <c r="F97">
-        <v>1.178770808773203</v>
+        <v>0.6644341749053785</v>
       </c>
       <c r="G97">
-        <v>-7.153106829008205</v>
+        <v>-5.271611240492055</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.667680587335357</v>
       </c>
       <c r="E98">
-        <v>-42.50449459334997</v>
+        <v>-42.19605343597654</v>
       </c>
       <c r="F98">
-        <v>0.6182907970998348</v>
+        <v>0.4915688085543721</v>
       </c>
       <c r="G98">
-        <v>-6.669694348272748</v>
+        <v>-5.156775036825816</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.025664939350609</v>
       </c>
       <c r="E99">
-        <v>-45.28372098252245</v>
+        <v>-44.42257051556482</v>
       </c>
       <c r="F99">
-        <v>0.4233038792570676</v>
+        <v>0.4634962656408996</v>
       </c>
       <c r="G99">
-        <v>-7.395908859949433</v>
+        <v>-5.452340542571948</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.440674216255529</v>
       </c>
       <c r="E100">
-        <v>-47.43769870121887</v>
+        <v>-47.02728989461472</v>
       </c>
       <c r="F100">
-        <v>0.5568723243866683</v>
+        <v>-0.1100462716072137</v>
       </c>
       <c r="G100">
-        <v>-7.822356783590651</v>
+        <v>-5.82793848672996</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.867002610535558</v>
       </c>
       <c r="E101">
-        <v>-49.29541346126697</v>
+        <v>-49.09485980077078</v>
       </c>
       <c r="F101">
-        <v>0.3885339858919611</v>
+        <v>0.073465272604572</v>
       </c>
       <c r="G101">
-        <v>-8.09630773751088</v>
+        <v>-6.12750975257861</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.362332489120327</v>
       </c>
       <c r="E102">
-        <v>-51.75445183149011</v>
+        <v>-51.08897899064093</v>
       </c>
       <c r="F102">
-        <v>0.09062076151654977</v>
+        <v>-0.5745516359922308</v>
       </c>
       <c r="G102">
-        <v>-9.158929955251686</v>
+        <v>-6.001324998803749</v>
       </c>
     </row>
   </sheetData>
